--- a/src/ii_skills/shared/excel_templates/10_gantt_chart.xlsx
+++ b/src/ii_skills/shared/excel_templates/10_gantt_chart.xlsx
@@ -29,13 +29,15 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="0001395D"/>
+      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,8 +46,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A4A4A"/>
-        <bgColor rgb="004A4A4A"/>
+        <fgColor rgb="0001395D"/>
+        <bgColor rgb="0001395D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000A651"/>
+        <bgColor rgb="0000A651"/>
       </patternFill>
     </fill>
   </fills>
@@ -61,16 +69,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,256 +443,145 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1"/>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Timeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Workstream</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Start_Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>End_Date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Duration_Weeks</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>End</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Duration (Weeks)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Is_Milestone</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>MILESTONES</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="C5" s="3" t="n">
         <v>45658</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>45747</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="E5" t="n">
         <v>13</v>
       </c>
-      <c r="E2" s="1" t="b">
+      <c r="F5" t="b">
         <v>0</v>
       </c>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>Milestone_Name</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>Target_Date</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Appraisals</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>45672</v>
-      </c>
-      <c r="C3" s="4" t="n">
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Due Diligence</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>45689</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>45808</v>
+      </c>
+      <c r="E6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>45748</v>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>45838</v>
       </c>
-      <c r="D3" t="n">
-        <v>24</v>
-      </c>
-      <c r="E3" t="b">
+      <c r="E7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F7" t="b">
         <v>0</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Board Approval</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>45731</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Internal approval</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Due Diligence</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>45748</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>45930</v>
-      </c>
-      <c r="D4" t="n">
-        <v>26</v>
-      </c>
-      <c r="E4" t="b">
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>45778</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="E8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F8" t="b">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Prospectus Filed</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>45945</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Regulatory filing</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Structuring</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>45809</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>45930</v>
-      </c>
-      <c r="D5" t="n">
-        <v>17</v>
-      </c>
-      <c r="E5" t="b">
+    </row>
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>45870</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>45870</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>IPO Launch</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>45992</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Market debut</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Prospectus</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>45870</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>45991</v>
-      </c>
-      <c r="D6" t="n">
-        <v>17</v>
-      </c>
-      <c r="E6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>45931</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>45991</v>
-      </c>
-      <c r="D7" t="n">
-        <v>9</v>
-      </c>
-      <c r="E7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Filing</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>45945</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>45976</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Launch</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>45992</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>45992</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="b">
+      <c r="F9" s="4" t="b">
         <v>1</v>
       </c>
     </row>
